--- a/information_request_forms/020_customer_account_merge_contact_form--information_request_forms.xlsx
+++ b/information_request_forms/020_customer_account_merge_contact_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>merge_type1</t>
+          <t>merge type1</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>merge_type2</t>
+          <t>merge type2</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>merge_type3</t>
+          <t>merge type3</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>merge_type4</t>
+          <t>merge type4</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>merge_type5</t>
+          <t>merge type5</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>merge_type6</t>
+          <t>merge type6</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>merge_type7</t>
+          <t>merge type7</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>merge_type8</t>
+          <t>merge type8</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>merge_type9</t>
+          <t>merge type9</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>merge_type1</t>
+          <t>merge type1</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>merge_type2</t>
+          <t>merge type2</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>merge_type3</t>
+          <t>merge type3</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>merge_type4</t>
+          <t>merge type4</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>merge_type5</t>
+          <t>merge type5</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>merge_type6</t>
+          <t>merge type6</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>merge_type7</t>
+          <t>merge type7</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>merge_type8</t>
+          <t>merge type8</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>merge_type9</t>
+          <t>merge type9</t>
         </is>
       </c>
     </row>
